--- a/Data/Antimicrobial_of_honey.xlsx
+++ b/Data/Antimicrobial_of_honey.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Antimicrobial" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Antimicrobial_2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Antimicrobial_1" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="31">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -32,9 +32,15 @@
     <t xml:space="preserve">E_coli_75</t>
   </si>
   <si>
+    <t xml:space="preserve">K_pneumonia_50</t>
+  </si>
+  <si>
     <t xml:space="preserve">K_pneumonia_75</t>
   </si>
   <si>
+    <t xml:space="preserve">K_pneumonia_100</t>
+  </si>
+  <si>
     <t xml:space="preserve">P_mirabilis_50</t>
   </si>
   <si>
@@ -81,6 +87,33 @@
   </si>
   <si>
     <t xml:space="preserve">RYTA006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T. angustula ATA001 (3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T. angustula ER001 (2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. fuscopilosa FIED001 (7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. fasciculata RGB004 (6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. fuscopilosa RGY001 (8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. fuscopilosa RIG003 (9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. fasciculata RIG005 (5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. fasciculata RYMG001 (4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T. angustula RYTA006 (1)</t>
   </si>
 </sst>
 </file>
@@ -156,8 +189,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -178,13 +215,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="10.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1019" min="1" style="0" width="10.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1020" style="0" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -218,10 +256,16 @@
       <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>10</v>
@@ -233,100 +277,118 @@
         <v>9</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>9.5</v>
       </c>
-      <c r="J2" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="K2" s="0" t="n">
+      <c r="L2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" s="0" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="J3" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <v>12.5</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="H4" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H3" s="0" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="0" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K3" s="0" t="n">
+      <c r="J4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="0" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>14.8</v>
@@ -335,33 +397,39 @@
         <v>14.2</v>
       </c>
       <c r="D5" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <v>13.1</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="F5" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <v>14.7</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="H5" s="0" t="n">
         <v>15.9</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="I5" s="0" t="n">
         <v>17.6</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="J5" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="K5" s="0" t="n">
         <v>18.2</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="L5" s="0" t="n">
         <v>20.4</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="M5" s="0" t="n">
         <v>16.8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>15.1</v>
@@ -370,33 +438,39 @@
         <v>14.8</v>
       </c>
       <c r="D6" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <v>13.6</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="F6" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <v>14.8</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="H6" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="I6" s="0" t="n">
         <v>16.5</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="J6" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="K6" s="0" t="n">
         <v>17.4</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="L6" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="M6" s="0" t="n">
         <v>18.6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>17.1</v>
@@ -405,33 +479,39 @@
         <v>14.2</v>
       </c>
       <c r="D7" s="0" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="F7" s="0" t="n">
         <v>14.5</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="G7" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <v>17.7</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="I7" s="0" t="n">
         <v>18.5</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="J7" s="0" t="n">
         <v>9.3</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="K7" s="0" t="n">
         <v>16.6</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="L7" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="M7" s="0" t="n">
         <v>18.8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>12</v>
@@ -443,10 +523,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="G8" s="0" t="n">
         <v>14</v>
@@ -455,18 +535,24 @@
         <v>15</v>
       </c>
       <c r="I8" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="L8" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="M8" s="0" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>12.5</v>
@@ -475,13 +561,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="G9" s="0" t="n">
         <v>14</v>
@@ -490,18 +576,24 @@
         <v>14</v>
       </c>
       <c r="I9" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>17.5</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="L9" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="M9" s="0" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>12.5</v>
@@ -510,33 +602,39 @@
         <v>12</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="J10" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="K10" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="L10" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="M10" s="0" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>12.4</v>
@@ -545,33 +643,39 @@
         <v>11.4</v>
       </c>
       <c r="D11" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E11" s="0" t="n">
         <v>12.5</v>
       </c>
-      <c r="E11" s="0" t="n">
-        <v>14.8</v>
-      </c>
       <c r="F11" s="0" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="G11" s="0" t="n">
         <v>14.8</v>
       </c>
       <c r="H11" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J11" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="K11" s="0" t="n">
         <v>21.2</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="L11" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="M11" s="0" t="n">
         <v>19.5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>10.9</v>
@@ -586,27 +690,33 @@
         <v>12.9</v>
       </c>
       <c r="F12" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <v>13.9</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="I12" s="0" t="n">
         <v>14.6</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="J12" s="0" t="n">
         <v>18.5</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="K12" s="0" t="n">
         <v>20.4</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="L12" s="0" t="n">
         <v>20.8</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="M12" s="0" t="n">
         <v>19.2</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>11.3</v>
@@ -615,33 +725,39 @@
         <v>11.3</v>
       </c>
       <c r="D13" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <v>12.1</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="F13" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="H13" s="0" t="n">
         <v>14.4</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="I13" s="0" t="n">
         <v>14.9</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="J13" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="K13" s="0" t="n">
         <v>20.1</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="L13" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="M13" s="0" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>10</v>
@@ -650,33 +766,39 @@
         <v>8.7</v>
       </c>
       <c r="D14" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <v>8.4</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="F14" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <v>8.1</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="H14" s="0" t="n">
         <v>9.3</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="I14" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="J14" s="0" t="n">
         <v>6.7</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="K14" s="0" t="n">
         <v>8.1</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="L14" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="M14" s="0" t="n">
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>9.6</v>
@@ -685,33 +807,39 @@
         <v>8</v>
       </c>
       <c r="D15" s="0" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="F15" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="H15" s="0" t="n">
         <v>9.3</v>
       </c>
-      <c r="G15" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="0" t="n">
+      <c r="I15" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="0" t="n">
         <v>7.7</v>
       </c>
-      <c r="I15" s="0" t="n">
+      <c r="K15" s="0" t="n">
         <v>8.3</v>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="L15" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="M15" s="0" t="n">
         <v>10.4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>9.4</v>
@@ -720,33 +848,39 @@
         <v>8</v>
       </c>
       <c r="D16" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <v>8</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>8.9</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>9.2</v>
       </c>
       <c r="G16" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="I16" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="J16" s="0" t="n">
         <v>8.7</v>
       </c>
-      <c r="I16" s="0" t="n">
+      <c r="K16" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="L16" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="M16" s="0" t="n">
         <v>8.2</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>10</v>
@@ -755,33 +889,39 @@
         <v>9</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>9</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="J17" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I17" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" s="0" t="n">
+      <c r="K17" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="K17" s="0" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M17" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>10</v>
@@ -790,33 +930,39 @@
         <v>9</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>9</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="J18" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I18" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>14</v>
-      </c>
       <c r="K18" s="0" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="M18" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>10</v>
@@ -825,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="0" t="n">
         <v>9</v>
@@ -834,13 +980,13 @@
         <v>9</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J19" s="0" t="n">
         <v>13</v>
@@ -848,10 +994,16 @@
       <c r="K19" s="0" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L19" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>12.3</v>
@@ -860,33 +1012,39 @@
         <v>10.8</v>
       </c>
       <c r="D20" s="0" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="E20" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="F20" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G20" s="0" t="n">
         <v>9.8</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="H20" s="0" t="n">
         <v>11.5</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="I20" s="0" t="n">
         <v>13.6</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="J20" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="K20" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="L20" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="M20" s="0" t="n">
         <v>14.9</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>9.1</v>
@@ -895,33 +1053,39 @@
         <v>10.7</v>
       </c>
       <c r="D21" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E21" s="0" t="n">
         <v>7.7</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="F21" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="0" t="n">
         <v>10.1</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="H21" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="I21" s="0" t="n">
         <v>12.4</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="J21" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="I21" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" s="0" t="n">
+      <c r="K21" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L21" s="0" t="n">
         <v>13.4</v>
       </c>
-      <c r="K21" s="0" t="n">
+      <c r="M21" s="0" t="n">
         <v>15.7</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>11.3</v>
@@ -930,33 +1094,39 @@
         <v>11.4</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>8.6</v>
       </c>
       <c r="F22" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H22" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="G22" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="H22" s="0" t="n">
+      <c r="I22" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="I22" s="0" t="n">
+      <c r="K22" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="L22" s="0" t="n">
         <v>15.1</v>
       </c>
-      <c r="K22" s="0" t="n">
+      <c r="M22" s="0" t="n">
         <v>17.8</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>17.7</v>
@@ -965,33 +1135,39 @@
         <v>17.6</v>
       </c>
       <c r="D23" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E23" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="F23" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G23" s="0" t="n">
         <v>16.3</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="H23" s="0" t="n">
         <v>19.4</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="I23" s="0" t="n">
         <v>17.6</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="J23" s="0" t="n">
         <v>29.2</v>
       </c>
-      <c r="I23" s="0" t="n">
+      <c r="K23" s="0" t="n">
         <v>28.5</v>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="L23" s="0" t="n">
         <v>33.4</v>
       </c>
-      <c r="K23" s="0" t="n">
+      <c r="M23" s="0" t="n">
         <v>31.1</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>18.3</v>
@@ -1000,33 +1176,39 @@
         <v>17.5</v>
       </c>
       <c r="D24" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E24" s="0" t="n">
         <v>11.2</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="F24" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G24" s="0" t="n">
         <v>18.2</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="H24" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="I24" s="0" t="n">
         <v>19.2</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="J24" s="0" t="n">
         <v>28.5</v>
       </c>
-      <c r="I24" s="0" t="n">
+      <c r="K24" s="0" t="n">
         <v>30.5</v>
       </c>
-      <c r="J24" s="0" t="n">
+      <c r="L24" s="0" t="n">
         <v>33.6</v>
       </c>
-      <c r="K24" s="0" t="n">
+      <c r="M24" s="0" t="n">
         <v>31.9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>17.3</v>
@@ -1035,33 +1217,39 @@
         <v>16.8</v>
       </c>
       <c r="D25" s="0" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="E25" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="F25" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G25" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="H25" s="0" t="n">
         <v>18.3</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="I25" s="0" t="n">
         <v>19.2</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="J25" s="0" t="n">
         <v>28.2</v>
       </c>
-      <c r="I25" s="0" t="n">
+      <c r="K25" s="0" t="n">
         <v>30.6</v>
       </c>
-      <c r="J25" s="0" t="n">
+      <c r="L25" s="0" t="n">
         <v>34</v>
       </c>
-      <c r="K25" s="0" t="n">
+      <c r="M25" s="0" t="n">
         <v>33.4</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>12.3</v>
@@ -1070,33 +1258,39 @@
         <v>11.3</v>
       </c>
       <c r="D26" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="F26" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G26" s="0" t="n">
         <v>15.5</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="H26" s="0" t="n">
         <v>15.2</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="I26" s="0" t="n">
         <v>16.1</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="J26" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="I26" s="0" t="n">
+      <c r="K26" s="0" t="n">
         <v>16.7</v>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="L26" s="0" t="n">
         <v>18.2</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="M26" s="0" t="n">
         <v>20.3</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>13.8</v>
@@ -1105,33 +1299,39 @@
         <v>12.3</v>
       </c>
       <c r="D27" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" s="0" t="n">
         <v>12.3</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="F27" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G27" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="H27" s="0" t="n">
         <v>17.8</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="I27" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="J27" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="I27" s="0" t="n">
+      <c r="K27" s="0" t="n">
         <v>16.7</v>
       </c>
-      <c r="J27" s="0" t="n">
+      <c r="L27" s="0" t="n">
         <v>19.5</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="M27" s="0" t="n">
         <v>21.8</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>14.6</v>
@@ -1140,27 +1340,33 @@
         <v>12.1</v>
       </c>
       <c r="D28" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" s="0" t="n">
         <v>12.1</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="F28" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G28" s="0" t="n">
         <v>16.8</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="H28" s="0" t="n">
         <v>15.5</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="I28" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="J28" s="0" t="n">
         <v>10.9</v>
       </c>
-      <c r="I28" s="0" t="n">
+      <c r="K28" s="0" t="n">
         <v>15.6</v>
       </c>
-      <c r="J28" s="0" t="n">
+      <c r="L28" s="0" t="n">
         <v>19.6</v>
       </c>
-      <c r="K28" s="0" t="n">
+      <c r="M28" s="0" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1180,13 +1386,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="10.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1019" min="1" style="0" width="10.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1020" style="0" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -1220,97 +1427,139 @@
       <c r="K1" s="0" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="J3" s="0" t="n">
         <v>9.5</v>
       </c>
-      <c r="J2" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="K2" s="0" t="n">
+      <c r="K3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M3" s="0" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" s="0" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K3" s="0" t="n">
+      <c r="J4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="0" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>14.8</v>
@@ -1319,33 +1568,39 @@
         <v>14.2</v>
       </c>
       <c r="D5" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <v>13.1</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="F5" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="0" t="n">
         <v>14.7</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="H5" s="0" t="n">
         <v>15.9</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="I5" s="0" t="n">
         <v>17.6</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="J5" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="K5" s="0" t="n">
         <v>18.2</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="L5" s="0" t="n">
         <v>20.4</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="M5" s="0" t="n">
         <v>16.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>15.1</v>
@@ -1354,33 +1609,39 @@
         <v>14.8</v>
       </c>
       <c r="D6" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <v>13.6</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="F6" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G6" s="0" t="n">
         <v>14.8</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="H6" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="I6" s="0" t="n">
         <v>16.5</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="J6" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="I6" s="0" t="n">
+      <c r="K6" s="0" t="n">
         <v>17.4</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="L6" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="M6" s="0" t="n">
         <v>18.6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>17.1</v>
@@ -1389,33 +1650,39 @@
         <v>14.2</v>
       </c>
       <c r="D7" s="0" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="F7" s="0" t="n">
         <v>14.5</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="G7" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H7" s="0" t="n">
         <v>17.7</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="I7" s="0" t="n">
         <v>18.5</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="J7" s="0" t="n">
         <v>9.3</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="K7" s="0" t="n">
         <v>16.6</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="L7" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="M7" s="0" t="n">
         <v>18.8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>12</v>
@@ -1427,10 +1694,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="G8" s="0" t="n">
         <v>14</v>
@@ -1439,18 +1706,24 @@
         <v>15</v>
       </c>
       <c r="I8" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="L8" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="M8" s="0" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>12.5</v>
@@ -1459,13 +1732,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>14</v>
+        <v>9.5</v>
       </c>
       <c r="G9" s="0" t="n">
         <v>14</v>
@@ -1474,18 +1747,24 @@
         <v>14</v>
       </c>
       <c r="I9" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>17.5</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="L9" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="M9" s="0" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>12.5</v>
@@ -1494,33 +1773,39 @@
         <v>12</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="J10" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="K10" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="L10" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="M10" s="0" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>12.4</v>
@@ -1529,33 +1814,39 @@
         <v>11.4</v>
       </c>
       <c r="D11" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E11" s="0" t="n">
         <v>12.5</v>
       </c>
-      <c r="E11" s="0" t="n">
-        <v>14.8</v>
-      </c>
       <c r="F11" s="0" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="G11" s="0" t="n">
         <v>14.8</v>
       </c>
       <c r="H11" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J11" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="I11" s="0" t="n">
+      <c r="K11" s="0" t="n">
         <v>21.2</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="L11" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="M11" s="0" t="n">
         <v>19.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>10.9</v>
@@ -1570,27 +1861,33 @@
         <v>12.9</v>
       </c>
       <c r="F12" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <v>13.9</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="I12" s="0" t="n">
         <v>14.6</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="J12" s="0" t="n">
         <v>18.5</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="K12" s="0" t="n">
         <v>20.4</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="L12" s="0" t="n">
         <v>20.8</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="M12" s="0" t="n">
         <v>19.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>11.3</v>
@@ -1599,33 +1896,39 @@
         <v>11.3</v>
       </c>
       <c r="D13" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <v>12.1</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="F13" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G13" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="F13" s="0" t="n">
+      <c r="H13" s="0" t="n">
         <v>14.4</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="I13" s="0" t="n">
         <v>14.9</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="J13" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="K13" s="0" t="n">
         <v>20.1</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="L13" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="M13" s="0" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>10</v>
@@ -1634,33 +1937,39 @@
         <v>8.7</v>
       </c>
       <c r="D14" s="0" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <v>8.4</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="F14" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G14" s="0" t="n">
         <v>8.1</v>
       </c>
-      <c r="F14" s="0" t="n">
+      <c r="H14" s="0" t="n">
         <v>9.3</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="I14" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="J14" s="0" t="n">
         <v>6.7</v>
       </c>
-      <c r="I14" s="0" t="n">
+      <c r="K14" s="0" t="n">
         <v>8.1</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="L14" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="M14" s="0" t="n">
         <v>10.9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>9.6</v>
@@ -1669,33 +1978,39 @@
         <v>8</v>
       </c>
       <c r="D15" s="0" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="F15" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G15" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="F15" s="0" t="n">
+      <c r="H15" s="0" t="n">
         <v>9.3</v>
       </c>
-      <c r="G15" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" s="0" t="n">
+      <c r="I15" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="0" t="n">
         <v>7.7</v>
       </c>
-      <c r="I15" s="0" t="n">
+      <c r="K15" s="0" t="n">
         <v>8.3</v>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="L15" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="M15" s="0" t="n">
         <v>10.4</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>9.4</v>
@@ -1704,94 +2019,130 @@
         <v>8</v>
       </c>
       <c r="D16" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <v>8</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>8.9</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>9.2</v>
       </c>
       <c r="G16" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="I16" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="J16" s="0" t="n">
         <v>8.7</v>
       </c>
-      <c r="I16" s="0" t="n">
+      <c r="K16" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="L16" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="M16" s="0" t="n">
         <v>8.2</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>9</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="J17" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I17" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" s="0" t="n">
+      <c r="K17" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="M17" s="0" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>9</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H18" s="0" t="n">
+      <c r="J18" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I18" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" s="0" t="n">
-        <v>14</v>
-      </c>
       <c r="K18" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="M18" s="0" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>8</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="0" t="n">
         <v>9</v>
@@ -1800,13 +2151,13 @@
         <v>9</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H19" s="0" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J19" s="0" t="n">
         <v>13</v>
@@ -1814,10 +2165,16 @@
       <c r="K19" s="0" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L19" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>12.3</v>
@@ -1826,33 +2183,39 @@
         <v>10.8</v>
       </c>
       <c r="D20" s="0" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="E20" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="F20" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G20" s="0" t="n">
         <v>9.8</v>
       </c>
-      <c r="F20" s="0" t="n">
+      <c r="H20" s="0" t="n">
         <v>11.5</v>
       </c>
-      <c r="G20" s="0" t="n">
+      <c r="I20" s="0" t="n">
         <v>13.6</v>
       </c>
-      <c r="H20" s="0" t="n">
+      <c r="J20" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="I20" s="0" t="n">
+      <c r="K20" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="L20" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="M20" s="0" t="n">
         <v>14.9</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>9.1</v>
@@ -1861,33 +2224,39 @@
         <v>10.7</v>
       </c>
       <c r="D21" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E21" s="0" t="n">
         <v>7.7</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="F21" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="0" t="n">
         <v>10.1</v>
       </c>
-      <c r="F21" s="0" t="n">
+      <c r="H21" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="G21" s="0" t="n">
+      <c r="I21" s="0" t="n">
         <v>12.4</v>
       </c>
-      <c r="H21" s="0" t="n">
+      <c r="J21" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="I21" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" s="0" t="n">
+      <c r="K21" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L21" s="0" t="n">
         <v>13.4</v>
       </c>
-      <c r="K21" s="0" t="n">
+      <c r="M21" s="0" t="n">
         <v>15.7</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>11.3</v>
@@ -1896,33 +2265,39 @@
         <v>11.4</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>8.6</v>
+        <v>6.7</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>8.6</v>
       </c>
       <c r="F22" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H22" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="G22" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="H22" s="0" t="n">
+      <c r="I22" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="I22" s="0" t="n">
+      <c r="K22" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="L22" s="0" t="n">
         <v>15.1</v>
       </c>
-      <c r="K22" s="0" t="n">
+      <c r="M22" s="0" t="n">
         <v>17.8</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>17.7</v>
@@ -1931,24 +2306,39 @@
         <v>17.6</v>
       </c>
       <c r="D23" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E23" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="F23" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G23" s="0" t="n">
         <v>16.3</v>
       </c>
-      <c r="F23" s="0" t="n">
+      <c r="H23" s="0" t="n">
         <v>19.4</v>
       </c>
-      <c r="G23" s="0" t="n">
+      <c r="I23" s="0" t="n">
         <v>17.6</v>
       </c>
-      <c r="H23" s="0" t="n">
+      <c r="J23" s="0" t="n">
         <v>29.2</v>
+      </c>
+      <c r="K23" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>31.1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>18.3</v>
@@ -1957,24 +2347,39 @@
         <v>17.5</v>
       </c>
       <c r="D24" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E24" s="0" t="n">
         <v>11.2</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="F24" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G24" s="0" t="n">
         <v>18.2</v>
       </c>
-      <c r="F24" s="0" t="n">
+      <c r="H24" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="G24" s="0" t="n">
+      <c r="I24" s="0" t="n">
         <v>19.2</v>
       </c>
-      <c r="H24" s="0" t="n">
+      <c r="J24" s="0" t="n">
         <v>28.5</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>31.9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>17.3</v>
@@ -1983,24 +2388,39 @@
         <v>16.8</v>
       </c>
       <c r="D25" s="0" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="E25" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="F25" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G25" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="F25" s="0" t="n">
+      <c r="H25" s="0" t="n">
         <v>18.3</v>
       </c>
-      <c r="G25" s="0" t="n">
+      <c r="I25" s="0" t="n">
         <v>19.2</v>
       </c>
-      <c r="H25" s="0" t="n">
+      <c r="J25" s="0" t="n">
         <v>28.2</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K25" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="L25" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>12.3</v>
@@ -2009,33 +2429,39 @@
         <v>11.3</v>
       </c>
       <c r="D26" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="F26" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G26" s="0" t="n">
         <v>15.5</v>
       </c>
-      <c r="F26" s="0" t="n">
+      <c r="H26" s="0" t="n">
         <v>15.2</v>
       </c>
-      <c r="G26" s="0" t="n">
+      <c r="I26" s="0" t="n">
         <v>16.1</v>
       </c>
-      <c r="H26" s="0" t="n">
+      <c r="J26" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="I26" s="0" t="n">
+      <c r="K26" s="0" t="n">
         <v>16.7</v>
       </c>
-      <c r="J26" s="0" t="n">
+      <c r="L26" s="0" t="n">
         <v>18.2</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="M26" s="0" t="n">
         <v>20.3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>13.8</v>
@@ -2044,33 +2470,39 @@
         <v>12.3</v>
       </c>
       <c r="D27" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" s="0" t="n">
         <v>12.3</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="F27" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G27" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="H27" s="0" t="n">
         <v>17.8</v>
       </c>
-      <c r="G27" s="0" t="n">
+      <c r="I27" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="H27" s="0" t="n">
+      <c r="J27" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="I27" s="0" t="n">
+      <c r="K27" s="0" t="n">
         <v>16.7</v>
       </c>
-      <c r="J27" s="0" t="n">
+      <c r="L27" s="0" t="n">
         <v>19.5</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="M27" s="0" t="n">
         <v>21.8</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>14.6</v>
@@ -2079,27 +2511,33 @@
         <v>12.1</v>
       </c>
       <c r="D28" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" s="0" t="n">
         <v>12.1</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="F28" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G28" s="0" t="n">
         <v>16.8</v>
       </c>
-      <c r="F28" s="0" t="n">
+      <c r="H28" s="0" t="n">
         <v>15.5</v>
       </c>
-      <c r="G28" s="0" t="n">
+      <c r="I28" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="H28" s="0" t="n">
+      <c r="J28" s="0" t="n">
         <v>10.9</v>
       </c>
-      <c r="I28" s="0" t="n">
+      <c r="K28" s="0" t="n">
         <v>15.6</v>
       </c>
-      <c r="J28" s="0" t="n">
+      <c r="L28" s="0" t="n">
         <v>19.6</v>
       </c>
-      <c r="K28" s="0" t="n">
+      <c r="M28" s="0" t="n">
         <v>22</v>
       </c>
     </row>

--- a/Data/Antimicrobial_of_honey.xlsx
+++ b/Data/Antimicrobial_of_honey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Antimicrobial" sheetId="1" state="visible" r:id="rId2"/>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">M. fuscopilosa FIED001 (7)</t>
   </si>
   <si>
-    <t xml:space="preserve">M. fasciculata RGB004 (6)</t>
+    <t xml:space="preserve">M. grandis RGB004 (6)</t>
   </si>
   <si>
     <t xml:space="preserve">M. fuscopilosa RGY001 (8)</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">M. fuscopilosa RIG003 (9)</t>
   </si>
   <si>
-    <t xml:space="preserve">M. fasciculata RIG005 (5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M. fasciculata RYMG001 (4)</t>
+    <t xml:space="preserve">M. grandis RIG005 (5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M. grandis RYMG001 (4)</t>
   </si>
   <si>
     <t xml:space="preserve">T. angustula RYTA006 (1)</t>
